--- a/Tests/Validation/Barley/Observations/MCPD09_10Biomass.xlsx
+++ b/Tests/Validation/Barley/Observations/MCPD09_10Biomass.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubRepos\ApsimX\Prototypes\Barley\Observations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Repos\ApsimX\Tests\Validation\Barley\Observations\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D64BB6-7D57-4188-B1ED-24B6926A788A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15750" windowHeight="22020"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,9 +34,6 @@
   </si>
   <si>
     <t>Barley.Leaf.LAI</t>
-  </si>
-  <si>
-    <t>Barley.Leaf.SLA</t>
   </si>
   <si>
     <t>Barley.Grain.Wt</t>
@@ -121,11 +119,14 @@
   <si>
     <t>Barley.AboveGround.Wt</t>
   </si>
+  <si>
+    <t>Barley.Leaf.SpecificAreaCanopy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -462,15 +463,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N208"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -481,42 +482,42 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
       </c>
       <c r="B2" s="3">
         <v>40121</v>
@@ -546,21 +547,21 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N2">
         <v>50.300000000000011</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3">
         <v>40151</v>
@@ -590,21 +591,21 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N3">
         <v>539.80000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3">
         <v>40159</v>
@@ -634,21 +635,21 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N4">
         <v>635.20000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3">
         <v>40165</v>
@@ -678,21 +679,21 @@
         <v>121.94275178287526</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N5">
         <v>894.39202516069838</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3">
         <v>40175</v>
@@ -722,21 +723,21 @@
         <v>121.94275178287526</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N6">
         <v>1200.8932472991073</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3">
         <v>40184</v>
@@ -766,21 +767,21 @@
         <v>121.94275178287526</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N7">
         <v>1501.3315291949743</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3">
         <v>40196</v>
@@ -810,21 +811,21 @@
         <v>121.94275178287526</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N8">
         <v>1642.1268752243395</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3">
         <v>40206</v>
@@ -854,21 +855,21 @@
         <v>121.94275178287523</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N9">
         <v>1976.175649252149</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3">
         <v>40231</v>
@@ -904,15 +905,15 @@
         <v>24559.078440956273</v>
       </c>
       <c r="M10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N10">
         <v>1765.717327196825</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="3">
         <v>40121</v>
@@ -942,21 +943,21 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N11">
         <v>36.5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3">
         <v>40127</v>
@@ -986,21 +987,21 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N12">
         <v>95.950000000000017</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="3">
         <v>40133</v>
@@ -1030,21 +1031,21 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N13">
         <v>147.92500000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3">
         <v>40137</v>
@@ -1074,21 +1075,21 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N14">
         <v>253.25</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3">
         <v>40141</v>
@@ -1118,21 +1119,21 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N15">
         <v>327.07500000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
         <v>40144</v>
@@ -1162,21 +1163,21 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N16">
         <v>370.15</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
         <v>40151</v>
@@ -1206,21 +1207,21 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N17">
         <v>507.69999999999993</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="3">
         <v>40159</v>
@@ -1250,21 +1251,21 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N18">
         <v>703.32500000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="3">
         <v>40165</v>
@@ -1294,21 +1295,21 @@
         <v>98.37122975925385</v>
       </c>
       <c r="K19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N19">
         <v>783.43486817508619</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="3">
         <v>40175</v>
@@ -1338,21 +1339,21 @@
         <v>98.37122975925385</v>
       </c>
       <c r="K20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N20">
         <v>1198.9411427012983</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="3">
         <v>40184</v>
@@ -1382,21 +1383,21 @@
         <v>98.37122975925385</v>
       </c>
       <c r="K21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N21">
         <v>1318.0389320912166</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="3">
         <v>40196</v>
@@ -1426,21 +1427,21 @@
         <v>98.37122975925385</v>
       </c>
       <c r="K22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N22">
         <v>1243.4380161748782</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3">
         <v>40206</v>
@@ -1470,21 +1471,21 @@
         <v>98.37122975925385</v>
       </c>
       <c r="K23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N23">
         <v>1543.1668026061689</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="3">
         <v>40231</v>
@@ -1520,15 +1521,15 @@
         <v>17597.195535013048</v>
       </c>
       <c r="M24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N24">
         <v>1350.6593431214469</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B25" s="3">
         <v>40127</v>
@@ -1558,21 +1559,21 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N25">
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="3">
         <v>40133</v>
@@ -1602,21 +1603,21 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N26">
         <v>111.7</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="3">
         <v>40137</v>
@@ -1646,21 +1647,21 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N27">
         <v>204</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="3">
         <v>40141</v>
@@ -1690,21 +1691,21 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N28">
         <v>366.29999999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="3">
         <v>40144</v>
@@ -1734,21 +1735,21 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N29">
         <v>301.8</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="3">
         <v>40151</v>
@@ -1778,21 +1779,21 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N30">
         <v>477.42500000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" s="3">
         <v>40159</v>
@@ -1822,21 +1823,21 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N31">
         <v>707.90000000000009</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" s="3">
         <v>40165</v>
@@ -1866,21 +1867,21 @@
         <v>91.434147230134528</v>
       </c>
       <c r="K32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N32">
         <v>703.57837470181471</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33" s="3">
         <v>40175</v>
@@ -1910,21 +1911,21 @@
         <v>95.510963380793072</v>
       </c>
       <c r="K33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N33">
         <v>1204.2170146951705</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34" s="3">
         <v>40184</v>
@@ -1954,21 +1955,21 @@
         <v>95.510963380793086</v>
       </c>
       <c r="K34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N34">
         <v>1479.5162147394635</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35" s="3">
         <v>40196</v>
@@ -1998,21 +1999,21 @@
         <v>95.510963380793086</v>
       </c>
       <c r="K35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N35">
         <v>1370.486619751113</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B36" s="3">
         <v>40206</v>
@@ -2042,21 +2043,21 @@
         <v>95.510963380793086</v>
       </c>
       <c r="K36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N36">
         <v>1865.6804672472083</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37" s="3">
         <v>40231</v>
@@ -2092,15 +2093,15 @@
         <v>21527.366187036354</v>
       </c>
       <c r="M37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N37">
         <v>1486.3316741931194</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38" s="3">
         <v>40121</v>
@@ -2130,21 +2131,21 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N38">
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B39" s="3">
         <v>40127</v>
@@ -2174,21 +2175,21 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N39">
         <v>62.333333333333336</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" s="3">
         <v>40133</v>
@@ -2218,21 +2219,21 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N40">
         <v>113.83333333333334</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B41" s="3">
         <v>40137</v>
@@ -2262,21 +2263,21 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N41">
         <v>202.33333333333331</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B42" s="3">
         <v>40141</v>
@@ -2306,21 +2307,21 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N42">
         <v>273.96666666666664</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B43" s="3">
         <v>40144</v>
@@ -2350,21 +2351,21 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N43">
         <v>296.2</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" s="3">
         <v>40151</v>
@@ -2394,21 +2395,21 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N44">
         <v>407.15000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" s="3">
         <v>40159</v>
@@ -2438,21 +2439,21 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N45">
         <v>610.27500000000009</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B46" s="3">
         <v>40165</v>
@@ -2482,21 +2483,21 @@
         <v>85.308057689663784</v>
       </c>
       <c r="K46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N46">
         <v>859.90172688850669</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B47" s="3">
         <v>40175</v>
@@ -2526,21 +2527,21 @@
         <v>85.308057689663769</v>
       </c>
       <c r="K47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N47">
         <v>989.76431704289098</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B48" s="3">
         <v>40184</v>
@@ -2570,21 +2571,21 @@
         <v>85.308057689663769</v>
       </c>
       <c r="K48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N48">
         <v>1133.8335993862991</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B49" s="3">
         <v>40196</v>
@@ -2614,21 +2615,21 @@
         <v>85.308057689663769</v>
       </c>
       <c r="K49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N49">
         <v>1358.2499419742539</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B50" s="3">
         <v>40206</v>
@@ -2658,21 +2659,21 @@
         <v>85.308057689663769</v>
       </c>
       <c r="K50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N50">
         <v>1659.5970795905387</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B51" s="3">
         <v>40231</v>
@@ -2708,15 +2709,15 @@
         <v>19261.684002939797</v>
       </c>
       <c r="M51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N51">
         <v>1423.2157261104735</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B52" s="3">
         <v>40121</v>
@@ -2746,21 +2747,21 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N52">
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B53" s="3">
         <v>40127</v>
@@ -2790,21 +2791,21 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N53">
         <v>99.1</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B54" s="3">
         <v>40133</v>
@@ -2834,21 +2835,21 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N54">
         <v>148</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B55" s="3">
         <v>40137</v>
@@ -2878,21 +2879,21 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N55">
         <v>215.99999999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B56" s="3">
         <v>40141</v>
@@ -2922,21 +2923,21 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N56">
         <v>268.10000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B57" s="3">
         <v>40144</v>
@@ -2966,21 +2967,21 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N57">
         <v>367.99999999999994</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B58" s="3">
         <v>40151</v>
@@ -3010,21 +3011,21 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N58">
         <v>478.85</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B59" s="3">
         <v>40159</v>
@@ -3054,21 +3055,21 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N59">
         <v>727.65000000000009</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B60" s="3">
         <v>40165</v>
@@ -3098,21 +3099,21 @@
         <v>96.292953959753177</v>
       </c>
       <c r="K60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N60">
         <v>882.21356479273993</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B61" s="3">
         <v>40175</v>
@@ -3142,21 +3143,21 @@
         <v>96.292953959753191</v>
       </c>
       <c r="K61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N61">
         <v>1216.007202314006</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B62" s="3">
         <v>40184</v>
@@ -3186,21 +3187,21 @@
         <v>96.292953959753191</v>
       </c>
       <c r="K62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N62">
         <v>1453.765184264701</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B63" s="3">
         <v>40196</v>
@@ -3230,21 +3231,21 @@
         <v>96.292953959753191</v>
       </c>
       <c r="K63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N63">
         <v>1532.3203330393374</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B64" s="3">
         <v>40206</v>
@@ -3274,21 +3275,21 @@
         <v>96.292953959753177</v>
       </c>
       <c r="K64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N64">
         <v>2112.7400826923513</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B65" s="3">
         <v>40231</v>
@@ -3324,15 +3325,15 @@
         <v>22608.214752650871</v>
       </c>
       <c r="M65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N65">
         <v>1646.7397586440998</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B66" s="3">
         <v>40127</v>
@@ -3362,21 +3363,21 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N66">
         <v>84.6</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B67" s="3">
         <v>40133</v>
@@ -3406,21 +3407,21 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N67">
         <v>146.16666666666666</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B68" s="3">
         <v>40137</v>
@@ -3450,21 +3451,21 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N68">
         <v>237.33333333333334</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B69" s="3">
         <v>40141</v>
@@ -3494,21 +3495,21 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N69">
         <v>280.89999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B70" s="3">
         <v>40144</v>
@@ -3538,21 +3539,21 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N70">
         <v>398.30000000000007</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B71" s="3">
         <v>40151</v>
@@ -3582,21 +3583,21 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N71">
         <v>462.67500000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B72" s="3">
         <v>40159</v>
@@ -3626,21 +3627,21 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N72">
         <v>698.8</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B73" s="3">
         <v>40165</v>
@@ -3670,21 +3671,21 @@
         <v>94.380289516593763</v>
       </c>
       <c r="K73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N73">
         <v>796.42769779223613</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B74" s="3">
         <v>40175</v>
@@ -3714,21 +3715,21 @@
         <v>94.380289516593749</v>
       </c>
       <c r="K74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N74">
         <v>997.10948226787173</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B75" s="3">
         <v>40184</v>
@@ -3758,21 +3759,21 @@
         <v>94.380289516593749</v>
       </c>
       <c r="K75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N75">
         <v>1230.3921864768943</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B76" s="3">
         <v>40196</v>
@@ -3802,21 +3803,21 @@
         <v>94.380289516593763</v>
       </c>
       <c r="K76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N76">
         <v>1389.2900498947652</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B77" s="3">
         <v>40206</v>
@@ -3846,21 +3847,21 @@
         <v>94.380289516593763</v>
       </c>
       <c r="K77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N77">
         <v>1400.3833720330101</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B78" s="3">
         <v>40231</v>
@@ -3896,15 +3897,15 @@
         <v>19854.43932721973</v>
       </c>
       <c r="M78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N78">
         <v>1446.0082132999928</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B79" s="3">
         <v>40127</v>
@@ -3934,21 +3935,21 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N79">
         <v>85.800000000000011</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B80" s="3">
         <v>40133</v>
@@ -3978,21 +3979,21 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N80">
         <v>141.6</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B81" s="3">
         <v>40137</v>
@@ -4022,21 +4023,21 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N81">
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B82" s="3">
         <v>40141</v>
@@ -4066,21 +4067,21 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N82">
         <v>255.10000000000002</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B83" s="3">
         <v>40144</v>
@@ -4110,21 +4111,21 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N83">
         <v>358.90000000000003</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B84" s="3">
         <v>40151</v>
@@ -4154,21 +4155,21 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N84">
         <v>503.95000000000005</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B85" s="3">
         <v>40159</v>
@@ -4198,21 +4199,21 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N85">
         <v>688.77500000000009</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B86" s="3">
         <v>40165</v>
@@ -4242,21 +4243,21 @@
         <v>119.29054500130606</v>
       </c>
       <c r="K86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N86">
         <v>836.90376421369183</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B87" s="3">
         <v>40175</v>
@@ -4286,21 +4287,21 @@
         <v>119.29054500130606</v>
       </c>
       <c r="K87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N87">
         <v>1307.3768335373964</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B88" s="3">
         <v>40184</v>
@@ -4330,21 +4331,21 @@
         <v>119.29054500130607</v>
       </c>
       <c r="K88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N88">
         <v>1337.3023628599249</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B89" s="3">
         <v>40196</v>
@@ -4374,21 +4375,21 @@
         <v>119.29054500130607</v>
       </c>
       <c r="K89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N89">
         <v>1462.4627196608299</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B90" s="3">
         <v>40206</v>
@@ -4418,21 +4419,21 @@
         <v>119.29054500130606</v>
       </c>
       <c r="K90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N90">
         <v>1634.7565910699905</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B91" s="3">
         <v>40231</v>
@@ -4468,15 +4469,15 @@
         <v>20767.995778105273</v>
       </c>
       <c r="M91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N91">
         <v>1607.6195563079425</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B92" s="3">
         <v>40121</v>
@@ -4506,21 +4507,21 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N92">
         <v>45.7</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B93" s="3">
         <v>40127</v>
@@ -4550,21 +4551,21 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N93">
         <v>87.733333333333334</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B94" s="3">
         <v>40133</v>
@@ -4594,21 +4595,21 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L94" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M94" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N94">
         <v>164.86666666666667</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B95" s="3">
         <v>40137</v>
@@ -4638,21 +4639,21 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L95" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M95" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N95">
         <v>243</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B96" s="3">
         <v>40141</v>
@@ -4682,21 +4683,21 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N96">
         <v>243.39999999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B97" s="3">
         <v>40144</v>
@@ -4726,21 +4727,21 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N97">
         <v>368.80000000000007</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B98" s="3">
         <v>40151</v>
@@ -4770,21 +4771,21 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N98">
         <v>417.20000000000005</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B99" s="3">
         <v>40159</v>
@@ -4814,21 +4815,21 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N99">
         <v>610.07500000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B100" s="3">
         <v>40165</v>
@@ -4858,21 +4859,21 @@
         <v>99.445663492677355</v>
       </c>
       <c r="K100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N100">
         <v>881.65603485252075</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B101" s="3">
         <v>40175</v>
@@ -4902,21 +4903,21 @@
         <v>99.44566349267734</v>
       </c>
       <c r="K101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N101">
         <v>1137.1402818145211</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B102" s="3">
         <v>40184</v>
@@ -4946,21 +4947,21 @@
         <v>99.44566349267734</v>
       </c>
       <c r="K102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N102">
         <v>1290.6304493233606</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B103" s="3">
         <v>40196</v>
@@ -4990,21 +4991,21 @@
         <v>99.44566349267734</v>
       </c>
       <c r="K103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N103">
         <v>1464.7200951659813</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B104" s="3">
         <v>40206</v>
@@ -5034,21 +5035,21 @@
         <v>99.44566349267734</v>
       </c>
       <c r="K104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N104">
         <v>1632.9246625014416</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B105" s="3">
         <v>40231</v>
@@ -5084,15 +5085,15 @@
         <v>18693.436186816158</v>
       </c>
       <c r="M105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N105">
         <v>1430.6328288820337</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B106" s="3">
         <v>40121</v>
@@ -5122,21 +5123,21 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N106">
         <v>48.400000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B107" s="3">
         <v>40127</v>
@@ -5166,21 +5167,21 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N107">
         <v>103.89999999999999</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B108" s="3">
         <v>40133</v>
@@ -5210,21 +5211,21 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N108">
         <v>146.19999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B109" s="3">
         <v>40137</v>
@@ -5254,21 +5255,21 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N109">
         <v>235</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B110" s="3">
         <v>40141</v>
@@ -5298,21 +5299,21 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N110">
         <v>276.7</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B111" s="3">
         <v>40144</v>
@@ -5342,21 +5343,21 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N111">
         <v>369.19999999999993</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B112" s="3">
         <v>40151</v>
@@ -5386,21 +5387,21 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N112">
         <v>487.25</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B113" s="3">
         <v>40159</v>
@@ -5430,21 +5431,21 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N113">
         <v>694</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B114" s="3">
         <v>40165</v>
@@ -5474,21 +5475,21 @@
         <v>112.8448142878198</v>
       </c>
       <c r="K114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N114">
         <v>873.85701047809778</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B115" s="3">
         <v>40175</v>
@@ -5518,21 +5519,21 @@
         <v>112.8448142878198</v>
       </c>
       <c r="K115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N115">
         <v>1156.4261124448519</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B116" s="3">
         <v>40184</v>
@@ -5562,21 +5563,21 @@
         <v>112.84481428781983</v>
       </c>
       <c r="K116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N116">
         <v>1256.3932598418819</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B117" s="3">
         <v>40196</v>
@@ -5606,21 +5607,21 @@
         <v>112.8448142878198</v>
       </c>
       <c r="K117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N117">
         <v>1380.3375830450884</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B118" s="3">
         <v>40206</v>
@@ -5650,21 +5651,21 @@
         <v>112.84481428781979</v>
       </c>
       <c r="K118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N118">
         <v>1807.3067516351821</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B119" s="3">
         <v>40231</v>
@@ -5700,15 +5701,15 @@
         <v>19849.601730675153</v>
       </c>
       <c r="M119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N119">
         <v>1525.207059968847</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B120" s="3">
         <v>40121</v>
@@ -5738,21 +5739,21 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N120">
         <v>56.7</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B121" s="3">
         <v>40127</v>
@@ -5782,21 +5783,21 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N121">
         <v>90.066666666666677</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B122" s="3">
         <v>40133</v>
@@ -5826,21 +5827,21 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N122">
         <v>143.69999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B123" s="3">
         <v>40137</v>
@@ -5870,21 +5871,21 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N123">
         <v>184.66666666666666</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B124" s="3">
         <v>40141</v>
@@ -5914,21 +5915,21 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N124">
         <v>250.83333333333331</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B125" s="3">
         <v>40144</v>
@@ -5958,21 +5959,21 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N125">
         <v>317</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B126" s="3">
         <v>40151</v>
@@ -6002,21 +6003,21 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N126">
         <v>470.22499999999991</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B127" s="3">
         <v>40159</v>
@@ -6046,21 +6047,21 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N127">
         <v>648.59999999999991</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B128" s="3">
         <v>40165</v>
@@ -6090,21 +6091,21 @@
         <v>108.48907161487867</v>
       </c>
       <c r="K128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N128">
         <v>857.04525398456133</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B129" s="3">
         <v>40175</v>
@@ -6134,21 +6135,21 @@
         <v>108.48907161487864</v>
       </c>
       <c r="K129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N129">
         <v>1057.5285596587769</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B130" s="3">
         <v>40184</v>
@@ -6178,21 +6179,21 @@
         <v>108.48907161487868</v>
       </c>
       <c r="K130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N130">
         <v>1226.9571429669313</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B131" s="3">
         <v>40196</v>
@@ -6222,21 +6223,21 @@
         <v>108.48907161487867</v>
       </c>
       <c r="K131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N131">
         <v>1435.9435974203618</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B132" s="3">
         <v>40206</v>
@@ -6266,21 +6267,21 @@
         <v>108.48907161487867</v>
       </c>
       <c r="K132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N132">
         <v>1429.3098557999392</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B133" s="3">
         <v>40231</v>
@@ -6316,15 +6317,15 @@
         <v>18408.951869406064</v>
       </c>
       <c r="M133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N133">
         <v>1482.6312295235614</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B134" s="3">
         <v>40127</v>
@@ -6354,21 +6355,21 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N134">
         <v>112.8</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B135" s="3">
         <v>40133</v>
@@ -6398,21 +6399,21 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N135">
         <v>179.8</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B136" s="3">
         <v>40137</v>
@@ -6442,21 +6443,21 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N136">
         <v>273</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B137" s="3">
         <v>40141</v>
@@ -6486,21 +6487,21 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N137">
         <v>362.9</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B138" s="3">
         <v>40144</v>
@@ -6530,21 +6531,21 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N138">
         <v>437.6</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B139" s="3">
         <v>40151</v>
@@ -6574,21 +6575,21 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N139">
         <v>460.45000000000005</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B140" s="3">
         <v>40159</v>
@@ -6618,21 +6619,21 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N140">
         <v>644.92499999999995</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B141" s="3">
         <v>40165</v>
@@ -6662,21 +6663,21 @@
         <v>124.29725602491945</v>
       </c>
       <c r="K141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N141">
         <v>789.59248157155298</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B142" s="3">
         <v>40175</v>
@@ -6706,21 +6707,21 @@
         <v>124.35751233290641</v>
       </c>
       <c r="K142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N142">
         <v>1199.2126140398425</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B143" s="3">
         <v>40184</v>
@@ -6750,21 +6751,21 @@
         <v>124.35751233290641</v>
       </c>
       <c r="K143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N143">
         <v>1263.064798199119</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B144" s="3">
         <v>40196</v>
@@ -6794,21 +6795,21 @@
         <v>124.3575123329064</v>
       </c>
       <c r="K144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N144">
         <v>1264.1579469871403</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B145" s="3">
         <v>40206</v>
@@ -6838,21 +6839,21 @@
         <v>124.35751233290644</v>
       </c>
       <c r="K145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N145">
         <v>1709.6319480820484</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B146" s="3">
         <v>40231</v>
@@ -6888,15 +6889,15 @@
         <v>16045.211578826993</v>
       </c>
       <c r="M146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N146">
         <v>1424.3502822452051</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B147" s="3">
         <v>40121</v>
@@ -6926,21 +6927,21 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L147" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M147" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N147">
         <v>69.3</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B148" s="3">
         <v>40127</v>
@@ -6970,21 +6971,21 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L148" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M148" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N148">
         <v>86.799999999999983</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B149" s="3">
         <v>40133</v>
@@ -7014,21 +7015,21 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L149" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M149" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N149">
         <v>159.23333333333332</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B150" s="3">
         <v>40137</v>
@@ -7058,21 +7059,21 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N150">
         <v>267.33333333333337</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B151" s="3">
         <v>40141</v>
@@ -7102,21 +7103,21 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N151">
         <v>258.56666666666661</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B152" s="3">
         <v>40144</v>
@@ -7146,21 +7147,21 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N152">
         <v>393.16666666666674</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B153" s="3">
         <v>40151</v>
@@ -7190,21 +7191,21 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L153" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M153" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N153">
         <v>511.9</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B154" s="3">
         <v>40159</v>
@@ -7234,21 +7235,21 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N154">
         <v>742.97499999999991</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B155" s="3">
         <v>40165</v>
@@ -7278,21 +7279,21 @@
         <v>122.92247323242245</v>
       </c>
       <c r="K155" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L155" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M155" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N155">
         <v>817.10407995480239</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B156" s="3">
         <v>40175</v>
@@ -7322,21 +7323,21 @@
         <v>122.92247323242245</v>
       </c>
       <c r="K156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N156">
         <v>1167.1443260847284</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B157" s="3">
         <v>40184</v>
@@ -7366,21 +7367,21 @@
         <v>122.92247323242245</v>
       </c>
       <c r="K157" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L157" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M157" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N157">
         <v>1287.2927647830538</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B158" s="3">
         <v>40196</v>
@@ -7410,21 +7411,21 @@
         <v>122.92247323242245</v>
       </c>
       <c r="K158" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L158" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M158" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N158">
         <v>1408.7123142311441</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B159" s="3">
         <v>40206</v>
@@ -7454,21 +7455,21 @@
         <v>122.92247323242245</v>
       </c>
       <c r="K159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N159">
         <v>1934.6214909293485</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B160" s="3">
         <v>40231</v>
@@ -7504,15 +7505,15 @@
         <v>15795.849137574145</v>
       </c>
       <c r="M160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N160">
         <v>1451.7429921997164</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B161" s="3">
         <v>40127</v>
@@ -7542,21 +7543,21 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L161" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M161" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N161">
         <v>84.300000000000011</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B162" s="3">
         <v>40133</v>
@@ -7586,21 +7587,21 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L162" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M162" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N162">
         <v>193.60000000000002</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B163" s="3">
         <v>40137</v>
@@ -7630,21 +7631,21 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L163" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M163" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N163">
         <v>201.00000000000003</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B164" s="3">
         <v>40141</v>
@@ -7674,21 +7675,21 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L164" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M164" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N164">
         <v>358.09999999999997</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B165" s="3">
         <v>40144</v>
@@ -7718,21 +7719,21 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N165">
         <v>436.5</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B166" s="3">
         <v>40151</v>
@@ -7762,21 +7763,21 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L166" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M166" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N166">
         <v>510.15</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B167" s="3">
         <v>40159</v>
@@ -7806,21 +7807,21 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L167" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M167" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N167">
         <v>695.57499999999993</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B168" s="3">
         <v>40165</v>
@@ -7850,21 +7851,21 @@
         <v>108.2282549801153</v>
       </c>
       <c r="K168" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L168" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M168" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N168">
         <v>811.49372180017315</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B169" s="3">
         <v>40175</v>
@@ -7894,21 +7895,21 @@
         <v>108.2282549801153</v>
       </c>
       <c r="K169" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L169" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M169" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N169">
         <v>1177.6884181924725</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B170" s="3">
         <v>40184</v>
@@ -7938,21 +7939,21 @@
         <v>108.22825498011532</v>
       </c>
       <c r="K170" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L170" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M170" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N170">
         <v>1461.7011325422234</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B171" s="3">
         <v>40196</v>
@@ -7982,21 +7983,21 @@
         <v>108.2282549801153</v>
       </c>
       <c r="K171" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L171" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M171" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N171">
         <v>1432.6842122304627</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B172" s="3">
         <v>40206</v>
@@ -8026,21 +8027,21 @@
         <v>108.2282549801153</v>
       </c>
       <c r="K172" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L172" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M172" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N172">
         <v>1717.1647933280108</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B173" s="3">
         <v>40231</v>
@@ -8076,15 +8077,15 @@
         <v>21840.544483179718</v>
       </c>
       <c r="M173" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N173">
         <v>1659.3000610593656</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B174" s="3">
         <v>40121</v>
@@ -8114,21 +8115,21 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L174" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M174" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N174">
         <v>45.800000000000004</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B175" s="3">
         <v>40127</v>
@@ -8158,21 +8159,21 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L175" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M175" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N175">
         <v>71.033333333333331</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B176" s="3">
         <v>40133</v>
@@ -8202,21 +8203,21 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L176" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M176" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N176">
         <v>100.73333333333333</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B177" s="3">
         <v>40137</v>
@@ -8246,21 +8247,21 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L177" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M177" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N177">
         <v>181</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B178" s="3">
         <v>40141</v>
@@ -8290,21 +8291,21 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L178" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M178" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N178">
         <v>235.16666666666666</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B179" s="3">
         <v>40144</v>
@@ -8334,21 +8335,21 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L179" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M179" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N179">
         <v>262.43333333333334</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B180" s="3">
         <v>40151</v>
@@ -8378,21 +8379,21 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L180" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M180" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N180">
         <v>368.35</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B181" s="3">
         <v>40159</v>
@@ -8422,21 +8423,21 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N181">
         <v>532</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B182" s="3">
         <v>40165</v>
@@ -8466,21 +8467,21 @@
         <v>101.20151640561789</v>
       </c>
       <c r="K182" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L182" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M182" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N182">
         <v>743.27701244913521</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B183" s="3">
         <v>40175</v>
@@ -8510,21 +8511,21 @@
         <v>102.12580345798067</v>
       </c>
       <c r="K183" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L183" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M183" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N183">
         <v>1085.2109770157238</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B184" s="3">
         <v>40184</v>
@@ -8554,21 +8555,21 @@
         <v>102.12580345798067</v>
       </c>
       <c r="K184" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L184" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M184" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N184">
         <v>1128.0307065258091</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B185" s="3">
         <v>40196</v>
@@ -8598,21 +8599,21 @@
         <v>102.12580345798067</v>
       </c>
       <c r="K185" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L185" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M185" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N185">
         <v>1496.7503105105307</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B186" s="3">
         <v>40206</v>
@@ -8642,21 +8643,21 @@
         <v>102.12580345798065</v>
       </c>
       <c r="K186" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L186" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M186" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N186">
         <v>1510.260343632189</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B187" s="3">
         <v>40231</v>
@@ -8692,15 +8693,15 @@
         <v>19261.398325604951</v>
       </c>
       <c r="M187" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N187">
         <v>1476.3503954906214</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B188" s="3">
         <v>40121</v>
@@ -8730,21 +8731,21 @@
         <v>0</v>
       </c>
       <c r="K188" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L188" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M188" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N188">
         <v>49.25</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B189" s="3">
         <v>40151</v>
@@ -8774,21 +8775,21 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L189" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M189" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N189">
         <v>444.19999999999993</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B190" s="3">
         <v>40159</v>
@@ -8818,21 +8819,21 @@
         <v>0</v>
       </c>
       <c r="K190" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L190" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M190" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N190">
         <v>615.69999999999993</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B191" s="3">
         <v>40165</v>
@@ -8862,21 +8863,21 @@
         <v>112.75292757556981</v>
       </c>
       <c r="K191" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L191" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M191" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N191">
         <v>801.425275539621</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B192" s="3">
         <v>40175</v>
@@ -8906,21 +8907,21 @@
         <v>112.75292757556981</v>
       </c>
       <c r="K192" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L192" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M192" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N192">
         <v>1050.6427162471687</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B193" s="3">
         <v>40184</v>
@@ -8950,21 +8951,21 @@
         <v>112.75292757556983</v>
       </c>
       <c r="K193" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L193" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M193" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N193">
         <v>1202.7465138806447</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B194" s="3">
         <v>40196</v>
@@ -8994,21 +8995,21 @@
         <v>112.75292757556981</v>
       </c>
       <c r="K194" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L194" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M194" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N194">
         <v>1276.5482849547457</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B195" s="3">
         <v>40231</v>
@@ -9044,15 +9045,15 @@
         <v>19505.550643057923</v>
       </c>
       <c r="M195" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N195">
         <v>1391.2162190369563</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B196" s="3">
         <v>40121</v>
@@ -9082,21 +9083,21 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L196" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M196" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N196">
         <v>37.699999999999996</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B197" s="3">
         <v>40127</v>
@@ -9126,21 +9127,21 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L197" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M197" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N197">
         <v>72.449999999999989</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B198" s="3">
         <v>40133</v>
@@ -9170,21 +9171,21 @@
         <v>0</v>
       </c>
       <c r="K198" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L198" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M198" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N198">
         <v>126.92500000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B199" s="3">
         <v>40137</v>
@@ -9214,21 +9215,21 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L199" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M199" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N199">
         <v>184.75000000000003</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B200" s="3">
         <v>40141</v>
@@ -9258,21 +9259,21 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L200" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M200" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N200">
         <v>260.5</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B201" s="3">
         <v>40144</v>
@@ -9302,21 +9303,21 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N201">
         <v>342.47499999999997</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B202" s="3">
         <v>40151</v>
@@ -9346,21 +9347,21 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L202" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M202" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N202">
         <v>481.05000000000007</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B203" s="3">
         <v>40159</v>
@@ -9390,21 +9391,21 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L203" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M203" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N203">
         <v>554.92499999999995</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B204" s="3">
         <v>40165</v>
@@ -9434,21 +9435,21 @@
         <v>93.721675325909331</v>
       </c>
       <c r="K204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N204">
         <v>749.04651230158686</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B205" s="3">
         <v>40175</v>
@@ -9478,21 +9479,21 @@
         <v>93.721675325909331</v>
       </c>
       <c r="K205" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L205" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M205" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N205">
         <v>1086.1836389858665</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B206" s="3">
         <v>40184</v>
@@ -9522,21 +9523,21 @@
         <v>93.721675325909359</v>
       </c>
       <c r="K206" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L206" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M206" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N206">
         <v>1055.5981194933561</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B207" s="3">
         <v>40196</v>
@@ -9566,21 +9567,21 @@
         <v>93.721675325909331</v>
       </c>
       <c r="K207" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L207" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M207" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N207">
         <v>1208.4816041982911</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B208" s="3">
         <v>40231</v>
@@ -9616,7 +9617,7 @@
         <v>15658.399058186251</v>
       </c>
       <c r="M208" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N208">
         <v>1174.2742966462088</v>
